--- a/Data/collapsed database manual cases/zacatecas_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/zacatecas_collapsed_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E284B12-57AA-284E-9ECE-936740177DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A61293-0BA6-A44F-9FC0-BD727D2EC9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20720" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4480" yWindow="500" windowWidth="20720" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4635" uniqueCount="1073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4650" uniqueCount="1080">
   <si>
     <t>uniqueid</t>
   </si>
@@ -3242,6 +3242,27 @@
   </si>
   <si>
     <t>https://ieez.org.mx/MJ/acuerdos/sesiones/02012021_2/acuerdos/RCGIEEZ002VII2021_anexos/ANEXO1.pdf</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>SABINO DORADO RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>PP</t>
+  </si>
+  <si>
+    <t>OSCAR MEDINA PEREZ</t>
+  </si>
+  <si>
+    <t>FREDY GONZALEZ VAZQUEZ</t>
+  </si>
+  <si>
+    <t>SILVANO HASSAN GARDUÑO SERRANO</t>
+  </si>
+  <si>
+    <t>GUSTAVO AGUILAR ANDRADE</t>
   </si>
 </sst>
 </file>
@@ -3641,7 +3662,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S444"/>
+  <dimension ref="A1:S449"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
@@ -23326,6 +23347,91 @@
         <v>1072</v>
       </c>
     </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A445">
+        <v>32013</v>
+      </c>
+      <c r="B445">
+        <v>2021</v>
+      </c>
+      <c r="E445" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F445" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H445" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A446">
+        <v>32015</v>
+      </c>
+      <c r="B446">
+        <v>2024</v>
+      </c>
+      <c r="E446" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F446" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H446" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A447">
+        <v>32016</v>
+      </c>
+      <c r="B447">
+        <v>2024</v>
+      </c>
+      <c r="E447" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F447" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H447" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A448">
+        <v>32022</v>
+      </c>
+      <c r="B448">
+        <v>2024</v>
+      </c>
+      <c r="E448" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F448" t="s">
+        <v>1078</v>
+      </c>
+      <c r="H448" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A449">
+        <v>32024</v>
+      </c>
+      <c r="B449">
+        <v>2024</v>
+      </c>
+      <c r="E449" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F449" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H449" t="s">
+        <v>1075</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S404" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="5">
